--- a/Woche03/2026-10-14/[PRACTICE] WENN.xlsx
+++ b/Woche03/2026-10-14/[PRACTICE] WENN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dsinstitute-my.sharepoint.com/personal/yannik_rohrschneider_dsinstitute_de/Documents/Dokumente/Lehre/Excel/W3/01/Nachmittag/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSI\Python\Woche03\2026-10-14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{5C99B1BA-0A90-4965-878D-F8CE210311AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F7EB906-F369-4AB1-9EFF-B7E934166824}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375A9886-FA31-45CD-8555-6AD2BED0F14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Problem" sheetId="7" r:id="rId1"/>
@@ -117,8 +117,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="102">
   <si>
     <t>IF Function Excel Practice Exercises</t>
   </si>
@@ -430,12 +452,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="d\-mmm\-yy\ h:mm\ AM/PM"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.000"/>
     <numFmt numFmtId="168" formatCode="[$-409]d\-mmm;@"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -577,7 +600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -636,10 +659,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Überschrift 2" xfId="1" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Заголовок 2" xfId="1" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1582,27 +1611,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36509552-71BC-4F4A-8093-09EB1C5E63C3}">
   <dimension ref="B2:J126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="16.26953125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.54296875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.1796875" style="1"/>
+    <col min="14" max="14" width="13.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
@@ -1612,13 +1641,13 @@
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
     </row>
-    <row r="3" spans="2:10" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="20.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
@@ -1641,7 +1670,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
@@ -1657,12 +1686,13 @@
       <c r="F6" s="7">
         <v>6.99</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="8" t="str">
+        <f>IF(F6&lt;5,"Inklusive Steuer","")</f>
+        <v/>
+      </c>
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
@@ -1678,13 +1708,16 @@
       <c r="F7" s="7">
         <v>2.5</v>
       </c>
-      <c r="G7" s="8"/>
+      <c r="G7" s="8" t="str">
+        <f>IF(F7&lt;5,"Inklusive Steuer","")</f>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H7" s="15" t="s">
         <v>101</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
@@ -1700,12 +1733,15 @@
       <c r="F8" s="7">
         <v>8.99</v>
       </c>
-      <c r="G8" s="8"/>
+      <c r="G8" s="8" t="str">
+        <f>IF(F8&lt;5,"f32*0.1","")</f>
+        <v/>
+      </c>
       <c r="H8" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="6" t="s">
         <v>4</v>
       </c>
@@ -1721,12 +1757,15 @@
       <c r="F9" s="7">
         <v>12.99</v>
       </c>
-      <c r="G9" s="8"/>
+      <c r="G9" s="8" t="str">
+        <f t="shared" ref="G7:G28" si="0">IF(F9&lt;5,"Inklusive Steuer","")</f>
+        <v/>
+      </c>
       <c r="H9" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
@@ -1742,12 +1781,15 @@
       <c r="F10" s="7">
         <v>5.99</v>
       </c>
-      <c r="G10" s="8"/>
+      <c r="G10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H10" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="6" t="s">
         <v>6</v>
       </c>
@@ -1763,12 +1805,15 @@
       <c r="F11" s="7">
         <v>5.99</v>
       </c>
-      <c r="G11" s="8"/>
+      <c r="G11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H11" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
@@ -1784,12 +1829,15 @@
       <c r="F12" s="7">
         <v>5.99</v>
       </c>
-      <c r="G12" s="8"/>
+      <c r="G12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H12" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
@@ -1805,12 +1853,15 @@
       <c r="F13" s="7">
         <v>5.99</v>
       </c>
-      <c r="G13" s="8"/>
+      <c r="G13" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H13" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1826,12 +1877,15 @@
       <c r="F14" s="7">
         <v>5.99</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H14" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="6" t="s">
         <v>12</v>
       </c>
@@ -1847,12 +1901,15 @@
       <c r="F15" s="7">
         <v>7.99</v>
       </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H15" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
@@ -1868,12 +1925,15 @@
       <c r="F16" s="7">
         <v>2.99</v>
       </c>
-      <c r="G16" s="8"/>
+      <c r="G16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H16" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
@@ -1889,12 +1949,15 @@
       <c r="F17" s="7">
         <v>12.99</v>
       </c>
-      <c r="G17" s="8"/>
+      <c r="G17" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H17" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
@@ -1910,12 +1973,15 @@
       <c r="F18" s="7">
         <v>1.5</v>
       </c>
-      <c r="G18" s="8"/>
+      <c r="G18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H18" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="6" t="s">
         <v>16</v>
       </c>
@@ -1931,12 +1997,15 @@
       <c r="F19" s="7">
         <v>4.99</v>
       </c>
-      <c r="G19" s="8"/>
+      <c r="G19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H19" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="6" t="s">
         <v>17</v>
       </c>
@@ -1952,12 +2021,15 @@
       <c r="F20" s="7">
         <v>5.99</v>
       </c>
-      <c r="G20" s="8"/>
+      <c r="G20" s="8" t="str">
+        <f>IF(F20&lt;5,"Inklusive Steuer","")</f>
+        <v/>
+      </c>
       <c r="H20" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="6" t="s">
         <v>18</v>
       </c>
@@ -1973,12 +2045,15 @@
       <c r="F21" s="7">
         <v>12.99</v>
       </c>
-      <c r="G21" s="8"/>
+      <c r="G21" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H21" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
         <v>19</v>
       </c>
@@ -1994,12 +2069,15 @@
       <c r="F22" s="7">
         <v>9.99</v>
       </c>
-      <c r="G22" s="8"/>
+      <c r="G22" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H22" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="6" t="s">
         <v>20</v>
       </c>
@@ -2015,12 +2093,15 @@
       <c r="F23" s="7">
         <v>9.99</v>
       </c>
-      <c r="G23" s="8"/>
+      <c r="G23" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H23" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="6" t="s">
         <v>21</v>
       </c>
@@ -2036,12 +2117,15 @@
       <c r="F24" s="7">
         <v>2.99</v>
       </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H24" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
         <v>22</v>
       </c>
@@ -2057,12 +2141,15 @@
       <c r="F25" s="7">
         <v>1.99</v>
       </c>
-      <c r="G25" s="8"/>
+      <c r="G25" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H25" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="6" t="s">
         <v>23</v>
       </c>
@@ -2078,12 +2165,15 @@
       <c r="F26" s="7">
         <v>7.99</v>
       </c>
-      <c r="G26" s="8"/>
+      <c r="G26" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H26" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
@@ -2099,12 +2189,15 @@
       <c r="F27" s="7">
         <v>5.99</v>
       </c>
-      <c r="G27" s="8"/>
+      <c r="G27" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="H27" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="6" t="s">
         <v>25</v>
       </c>
@@ -2120,17 +2213,20 @@
       <c r="F28" s="7">
         <v>2.99</v>
       </c>
-      <c r="G28" s="8"/>
+      <c r="G28" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Inklusive Steuer</v>
+      </c>
       <c r="H28" s="15" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
         <v>42</v>
       </c>
@@ -2146,14 +2242,14 @@
       <c r="F31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="20" t="s">
         <v>44</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="6" t="s">
         <v>1</v>
       </c>
@@ -2169,12 +2265,15 @@
       <c r="F32" s="7">
         <v>6.99</v>
       </c>
-      <c r="G32" s="9"/>
+      <c r="G32" s="21" t="str">
+        <f>IF(F32&gt;5,"$"&amp;F32*0.1,"")</f>
+        <v>$0,699</v>
+      </c>
       <c r="H32" s="16">
         <v>0.69900000000000007</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="6" t="s">
         <v>2</v>
       </c>
@@ -2190,12 +2289,15 @@
       <c r="F33" s="7">
         <v>2.5</v>
       </c>
-      <c r="G33" s="9"/>
+      <c r="G33" s="21" t="str">
+        <f t="shared" ref="G33:G54" si="1">IF(F33&gt;5,"$"&amp;F33*0.1,"")</f>
+        <v/>
+      </c>
       <c r="H33" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="6" t="s">
         <v>3</v>
       </c>
@@ -2211,12 +2313,15 @@
       <c r="F34" s="7">
         <v>8.99</v>
       </c>
-      <c r="G34" s="9"/>
+      <c r="G34" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,899</v>
+      </c>
       <c r="H34" s="16">
         <v>0.89900000000000002</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="6" t="s">
         <v>4</v>
       </c>
@@ -2232,12 +2337,15 @@
       <c r="F35" s="7">
         <v>12.99</v>
       </c>
-      <c r="G35" s="9"/>
+      <c r="G35" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$1,299</v>
+      </c>
       <c r="H35" s="16">
         <v>1.2990000000000002</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="6" t="s">
         <v>5</v>
       </c>
@@ -2253,12 +2361,15 @@
       <c r="F36" s="7">
         <v>5.99</v>
       </c>
-      <c r="G36" s="9"/>
+      <c r="G36" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H36" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="37" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="6" t="s">
         <v>6</v>
       </c>
@@ -2274,12 +2385,15 @@
       <c r="F37" s="7">
         <v>5.99</v>
       </c>
-      <c r="G37" s="9"/>
+      <c r="G37" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H37" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="6" t="s">
         <v>9</v>
       </c>
@@ -2295,12 +2409,15 @@
       <c r="F38" s="7">
         <v>5.99</v>
       </c>
-      <c r="G38" s="9"/>
+      <c r="G38" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H38" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
@@ -2316,12 +2433,15 @@
       <c r="F39" s="7">
         <v>5.99</v>
       </c>
-      <c r="G39" s="9"/>
+      <c r="G39" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H39" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="6" t="s">
         <v>11</v>
       </c>
@@ -2337,12 +2457,15 @@
       <c r="F40" s="7">
         <v>5.99</v>
       </c>
-      <c r="G40" s="9"/>
+      <c r="G40" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H40" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="6" t="s">
         <v>12</v>
       </c>
@@ -2358,12 +2481,15 @@
       <c r="F41" s="7">
         <v>7.99</v>
       </c>
-      <c r="G41" s="9"/>
+      <c r="G41" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,799</v>
+      </c>
       <c r="H41" s="16">
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="6" t="s">
         <v>13</v>
       </c>
@@ -2379,12 +2505,15 @@
       <c r="F42" s="7">
         <v>2.99</v>
       </c>
-      <c r="G42" s="9"/>
+      <c r="G42" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="H42" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="6" t="s">
         <v>14</v>
       </c>
@@ -2400,12 +2529,15 @@
       <c r="F43" s="7">
         <v>12.99</v>
       </c>
-      <c r="G43" s="9"/>
+      <c r="G43" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$1,299</v>
+      </c>
       <c r="H43" s="16">
         <v>1.2990000000000002</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="6" t="s">
         <v>15</v>
       </c>
@@ -2421,12 +2553,15 @@
       <c r="F44" s="7">
         <v>1.5</v>
       </c>
-      <c r="G44" s="9"/>
+      <c r="G44" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="H44" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="6" t="s">
         <v>16</v>
       </c>
@@ -2442,12 +2577,15 @@
       <c r="F45" s="7">
         <v>4.99</v>
       </c>
-      <c r="G45" s="9"/>
+      <c r="G45" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="H45" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="6" t="s">
         <v>17</v>
       </c>
@@ -2463,12 +2601,15 @@
       <c r="F46" s="7">
         <v>5.99</v>
       </c>
-      <c r="G46" s="9"/>
+      <c r="G46" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H46" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="6" t="s">
         <v>18</v>
       </c>
@@ -2484,12 +2625,15 @@
       <c r="F47" s="7">
         <v>12.99</v>
       </c>
-      <c r="G47" s="9"/>
+      <c r="G47" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$1,299</v>
+      </c>
       <c r="H47" s="16">
         <v>1.2990000000000002</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="6" t="s">
         <v>19</v>
       </c>
@@ -2505,12 +2649,15 @@
       <c r="F48" s="7">
         <v>9.99</v>
       </c>
-      <c r="G48" s="9"/>
+      <c r="G48" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,999</v>
+      </c>
       <c r="H48" s="16">
         <v>0.99900000000000011</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="6" t="s">
         <v>20</v>
       </c>
@@ -2526,12 +2673,15 @@
       <c r="F49" s="7">
         <v>9.99</v>
       </c>
-      <c r="G49" s="9"/>
+      <c r="G49" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,999</v>
+      </c>
       <c r="H49" s="16">
         <v>0.99900000000000011</v>
       </c>
     </row>
-    <row r="50" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="6" t="s">
         <v>21</v>
       </c>
@@ -2547,12 +2697,15 @@
       <c r="F50" s="7">
         <v>2.99</v>
       </c>
-      <c r="G50" s="9"/>
+      <c r="G50" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="H50" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="6" t="s">
         <v>22</v>
       </c>
@@ -2568,12 +2721,15 @@
       <c r="F51" s="7">
         <v>1.99</v>
       </c>
-      <c r="G51" s="9"/>
+      <c r="G51" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="H51" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="6" t="s">
         <v>23</v>
       </c>
@@ -2589,12 +2745,15 @@
       <c r="F52" s="7">
         <v>7.99</v>
       </c>
-      <c r="G52" s="9"/>
+      <c r="G52" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,799</v>
+      </c>
       <c r="H52" s="16">
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="6" t="s">
         <v>24</v>
       </c>
@@ -2610,12 +2769,15 @@
       <c r="F53" s="7">
         <v>5.99</v>
       </c>
-      <c r="G53" s="9"/>
+      <c r="G53" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v>$0,599</v>
+      </c>
       <c r="H53" s="16">
         <v>0.59900000000000009</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="6" t="s">
         <v>25</v>
       </c>
@@ -2631,17 +2793,20 @@
       <c r="F54" s="7">
         <v>2.99</v>
       </c>
-      <c r="G54" s="9"/>
+      <c r="G54" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="H54" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="3" t="s">
         <v>42</v>
       </c>
@@ -2664,7 +2829,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="6" t="s">
         <v>1</v>
       </c>
@@ -2680,12 +2845,15 @@
       <c r="F58" s="7">
         <v>6.99</v>
       </c>
-      <c r="G58" s="9"/>
+      <c r="G58" s="9" t="str">
+        <f>IF(E58&lt;&gt;"Pizza", "", IF(F58&lt;7, "Small Pizza", IF(F58&lt;10, "Medium Pizza", "Large Pizza")))</f>
+        <v>Small Pizza</v>
+      </c>
       <c r="H58" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
@@ -2701,12 +2869,15 @@
       <c r="F59" s="7">
         <v>2.5</v>
       </c>
-      <c r="G59" s="9"/>
+      <c r="G59" s="9" t="str">
+        <f t="shared" ref="G59:G80" si="2">IF(E59&lt;&gt;"Pizza", "", IF(F59&lt;7, "Small Pizza", IF(F59&lt;10, "Medium Pizza", "Large Pizza")))</f>
+        <v/>
+      </c>
       <c r="H59" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="6" t="s">
         <v>3</v>
       </c>
@@ -2722,12 +2893,15 @@
       <c r="F60" s="7">
         <v>8.99</v>
       </c>
-      <c r="G60" s="9"/>
+      <c r="G60" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Medium Pizza</v>
+      </c>
       <c r="H60" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="6" t="s">
         <v>4</v>
       </c>
@@ -2743,12 +2917,15 @@
       <c r="F61" s="7">
         <v>12.99</v>
       </c>
-      <c r="G61" s="9"/>
+      <c r="G61" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Large Pizza</v>
+      </c>
       <c r="H61" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="6" t="s">
         <v>5</v>
       </c>
@@ -2764,12 +2941,15 @@
       <c r="F62" s="7">
         <v>5.99</v>
       </c>
-      <c r="G62" s="9"/>
+      <c r="G62" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H62" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="6" t="s">
         <v>6</v>
       </c>
@@ -2785,12 +2965,15 @@
       <c r="F63" s="7">
         <v>5.99</v>
       </c>
-      <c r="G63" s="9"/>
+      <c r="G63" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H63" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="6" t="s">
         <v>9</v>
       </c>
@@ -2806,12 +2989,15 @@
       <c r="F64" s="7">
         <v>5.99</v>
       </c>
-      <c r="G64" s="9"/>
+      <c r="G64" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H64" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="6" t="s">
         <v>10</v>
       </c>
@@ -2827,12 +3013,15 @@
       <c r="F65" s="7">
         <v>5.99</v>
       </c>
-      <c r="G65" s="9"/>
+      <c r="G65" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H65" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
@@ -2848,12 +3037,15 @@
       <c r="F66" s="7">
         <v>5.99</v>
       </c>
-      <c r="G66" s="9"/>
+      <c r="G66" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H66" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="6" t="s">
         <v>12</v>
       </c>
@@ -2869,12 +3061,15 @@
       <c r="F67" s="7">
         <v>7.99</v>
       </c>
-      <c r="G67" s="9"/>
+      <c r="G67" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H67" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="6" t="s">
         <v>13</v>
       </c>
@@ -2890,12 +3085,15 @@
       <c r="F68" s="7">
         <v>2.99</v>
       </c>
-      <c r="G68" s="9"/>
+      <c r="G68" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H68" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="6" t="s">
         <v>14</v>
       </c>
@@ -2911,12 +3109,15 @@
       <c r="F69" s="7">
         <v>12.99</v>
       </c>
-      <c r="G69" s="9"/>
+      <c r="G69" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Large Pizza</v>
+      </c>
       <c r="H69" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="70" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="6" t="s">
         <v>15</v>
       </c>
@@ -2932,12 +3133,15 @@
       <c r="F70" s="7">
         <v>1.5</v>
       </c>
-      <c r="G70" s="9"/>
+      <c r="G70" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H70" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B71" s="6" t="s">
         <v>16</v>
       </c>
@@ -2953,12 +3157,15 @@
       <c r="F71" s="7">
         <v>4.99</v>
       </c>
-      <c r="G71" s="9"/>
+      <c r="G71" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H71" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="6" t="s">
         <v>17</v>
       </c>
@@ -2974,12 +3181,15 @@
       <c r="F72" s="7">
         <v>5.99</v>
       </c>
-      <c r="G72" s="9"/>
+      <c r="G72" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H72" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="6" t="s">
         <v>18</v>
       </c>
@@ -2995,12 +3205,15 @@
       <c r="F73" s="7">
         <v>12.99</v>
       </c>
-      <c r="G73" s="9"/>
+      <c r="G73" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Large Pizza</v>
+      </c>
       <c r="H73" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="6" t="s">
         <v>19</v>
       </c>
@@ -3016,12 +3229,15 @@
       <c r="F74" s="7">
         <v>9.99</v>
       </c>
-      <c r="G74" s="9"/>
+      <c r="G74" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Medium Pizza</v>
+      </c>
       <c r="H74" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="75" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="6" t="s">
         <v>20</v>
       </c>
@@ -3037,12 +3253,15 @@
       <c r="F75" s="7">
         <v>9.99</v>
       </c>
-      <c r="G75" s="9"/>
+      <c r="G75" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Medium Pizza</v>
+      </c>
       <c r="H75" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="6" t="s">
         <v>21</v>
       </c>
@@ -3058,12 +3277,15 @@
       <c r="F76" s="7">
         <v>2.99</v>
       </c>
-      <c r="G76" s="9"/>
+      <c r="G76" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H76" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="77" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="6" t="s">
         <v>22</v>
       </c>
@@ -3079,12 +3301,15 @@
       <c r="F77" s="7">
         <v>1.99</v>
       </c>
-      <c r="G77" s="9"/>
+      <c r="G77" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H77" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="78" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="6" t="s">
         <v>23</v>
       </c>
@@ -3100,12 +3325,15 @@
       <c r="F78" s="7">
         <v>7.99</v>
       </c>
-      <c r="G78" s="9"/>
+      <c r="G78" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>Medium Pizza</v>
+      </c>
       <c r="H78" s="16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="79" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="6" t="s">
         <v>24</v>
       </c>
@@ -3121,12 +3349,15 @@
       <c r="F79" s="7">
         <v>5.99</v>
       </c>
-      <c r="G79" s="9"/>
+      <c r="G79" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H79" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="80" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="6" t="s">
         <v>25</v>
       </c>
@@ -3142,17 +3373,20 @@
       <c r="F80" s="7">
         <v>2.99</v>
       </c>
-      <c r="G80" s="9"/>
+      <c r="G80" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="H80" s="16" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="82" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B83" s="3" t="s">
         <v>85</v>
       </c>
@@ -3175,7 +3409,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="6">
         <v>1</v>
       </c>
@@ -3191,12 +3425,15 @@
       <c r="F84" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G84" s="12"/>
+      <c r="G84" s="12" cm="1">
+        <f t="array" ref="G84">IF(D84&gt;=1000000, 0.07, IF(D84&gt;=700000, 0.05, f(D84&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H84" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="6">
         <v>2</v>
       </c>
@@ -3212,12 +3449,15 @@
       <c r="F85" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G85" s="12"/>
+      <c r="G85" s="12" cm="1">
+        <f t="array" ref="G85">IF(D85&gt;=1000000, 0.07, IF(D85&gt;=700000, 0.05, f(D85&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H85" s="17">
         <v>0.03</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="6">
         <v>3</v>
       </c>
@@ -3233,12 +3473,15 @@
       <c r="F86" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G86" s="12"/>
+      <c r="G86" s="12" cm="1">
+        <f t="array" ref="G86">IF(D86&gt;=1000000, 0.07, IF(D86&gt;=700000, 0.05, f(D86&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H86" s="17">
         <v>0.03</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="6">
         <v>4</v>
       </c>
@@ -3254,12 +3497,15 @@
       <c r="F87" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G87" s="12"/>
+      <c r="G87" s="12" cm="1">
+        <f t="array" ref="G87">IF(D87&gt;=1000000, 0.07, IF(D87&gt;=700000, 0.05, f(D87&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H87" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="6">
         <v>5</v>
       </c>
@@ -3275,12 +3521,15 @@
       <c r="F88" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G88" s="12"/>
+      <c r="G88" s="12" cm="1">
+        <f t="array" ref="G88">IF(D88&gt;=1000000, 0.07, IF(D88&gt;=700000, 0.05, f(D88&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H88" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="6">
         <v>6</v>
       </c>
@@ -3296,12 +3545,15 @@
       <c r="F89" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G89" s="12"/>
+      <c r="G89" s="12" cm="1">
+        <f t="array" ref="G89">IF(D89&gt;=1000000, 0.07, IF(D89&gt;=700000, 0.05, f(D89&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H89" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="90" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B90" s="6">
         <v>7</v>
       </c>
@@ -3317,12 +3569,15 @@
       <c r="F90" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G90" s="12"/>
+      <c r="G90" s="12" cm="1">
+        <f t="array" ref="G90">IF(D90&gt;=1000000, 0.07, IF(D90&gt;=700000, 0.05, f(D90&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H90" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B91" s="6">
         <v>8</v>
       </c>
@@ -3338,12 +3593,15 @@
       <c r="F91" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G91" s="12"/>
+      <c r="G91" s="12" cm="1">
+        <f t="array" ref="G91">IF(D91&gt;=1000000, 0.07, IF(D91&gt;=700000, 0.05, f(D91&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H91" s="17">
         <v>0.05</v>
       </c>
     </row>
-    <row r="92" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B92" s="6">
         <v>9</v>
       </c>
@@ -3359,12 +3617,15 @@
       <c r="F92" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G92" s="12"/>
+      <c r="G92" s="12" cm="1">
+        <f t="array" ref="G92">IF(D92&gt;=1000000, 0.07, IF(D92&gt;=700000, 0.05, f(D92&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H92" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="93" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B93" s="6">
         <v>10</v>
       </c>
@@ -3380,12 +3641,15 @@
       <c r="F93" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G93" s="12"/>
+      <c r="G93" s="12" cm="1">
+        <f t="array" ref="G93">IF(D93&gt;=1000000, 0.07, IF(D93&gt;=700000, 0.05, f(D93&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H93" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="94" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B94" s="6">
         <v>11</v>
       </c>
@@ -3401,12 +3665,15 @@
       <c r="F94" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G94" s="12"/>
+      <c r="G94" s="12" cm="1">
+        <f t="array" ref="G94">IF(D94&gt;=1000000, 0.07, IF(D94&gt;=700000, 0.05, f(D94&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H94" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B95" s="6">
         <v>12</v>
       </c>
@@ -3422,12 +3689,15 @@
       <c r="F95" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G95" s="12"/>
+      <c r="G95" s="12" cm="1">
+        <f t="array" ref="G95">IF(D95&gt;=1000000, 0.07, IF(D95&gt;=700000, 0.05, f(D95&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H95" s="17">
         <v>0.05</v>
       </c>
     </row>
-    <row r="96" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B96" s="6">
         <v>13</v>
       </c>
@@ -3443,12 +3713,15 @@
       <c r="F96" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G96" s="12"/>
+      <c r="G96" s="12" cm="1">
+        <f t="array" ref="G96">IF(D96&gt;=1000000, 0.07, IF(D96&gt;=700000, 0.05, f(D96&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H96" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="97" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B97" s="6">
         <v>14</v>
       </c>
@@ -3464,12 +3737,15 @@
       <c r="F97" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G97" s="12"/>
+      <c r="G97" s="12" cm="1">
+        <f t="array" ref="G97">IF(D97&gt;=1000000, 0.07, IF(D97&gt;=700000, 0.05, f(D97&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H97" s="17">
         <v>0.05</v>
       </c>
     </row>
-    <row r="98" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="6">
         <v>15</v>
       </c>
@@ -3485,12 +3761,15 @@
       <c r="F98" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G98" s="12"/>
+      <c r="G98" s="12" cm="1">
+        <f t="array" ref="G98">IF(D98&gt;=1000000, 0.07, IF(D98&gt;=700000, 0.05, f(D98&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H98" s="17">
         <v>0.03</v>
       </c>
     </row>
-    <row r="99" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B99" s="6">
         <v>16</v>
       </c>
@@ -3506,12 +3785,15 @@
       <c r="F99" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G99" s="12"/>
+      <c r="G99" s="12" cm="1">
+        <f t="array" ref="G99">IF(D99&gt;=1000000, 0.07, IF(D99&gt;=700000, 0.05, f(D99&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H99" s="17">
         <v>0.03</v>
       </c>
     </row>
-    <row r="100" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B100" s="6">
         <v>17</v>
       </c>
@@ -3527,12 +3809,15 @@
       <c r="F100" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G100" s="12"/>
+      <c r="G100" s="12" cm="1">
+        <f t="array" ref="G100">IF(D100&gt;=1000000, 0.07, IF(D100&gt;=700000, 0.05, f(D100&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H100" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B101" s="6">
         <v>18</v>
       </c>
@@ -3548,12 +3833,15 @@
       <c r="F101" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G101" s="12"/>
+      <c r="G101" s="12" cm="1">
+        <f t="array" ref="G101">IF(D101&gt;=1000000, 0.07, IF(D101&gt;=700000, 0.05, f(D101&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H101" s="17">
         <v>0.05</v>
       </c>
     </row>
-    <row r="102" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B102" s="6">
         <v>19</v>
       </c>
@@ -3569,12 +3857,15 @@
       <c r="F102" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G102" s="12"/>
+      <c r="G102" s="12" cm="1">
+        <f t="array" ref="G102">IF(D102&gt;=1000000, 0.07, IF(D102&gt;=700000, 0.05, f(D102&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H102" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="6">
         <v>20</v>
       </c>
@@ -3590,21 +3881,24 @@
       <c r="F103" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G103" s="12"/>
+      <c r="G103" s="12" cm="1">
+        <f t="array" ref="G103">IF(D103&gt;=1000000, 0.07, IF(D103&gt;=700000, 0.05, f(D103&gt;=500000, 0.03, 0)))</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="H103" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H104" s="18"/>
     </row>
-    <row r="105" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B105" s="13" t="s">
         <v>99</v>
       </c>
       <c r="H105" s="18"/>
     </row>
-    <row r="106" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B106" s="3" t="s">
         <v>47</v>
       </c>
@@ -3627,7 +3921,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="107" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B107" s="6" t="s">
         <v>26</v>
       </c>
@@ -3643,12 +3937,15 @@
       <c r="F107" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G107" s="12"/>
+      <c r="G107" s="12" t="str">
+        <f>IF(E107&gt;=90, "A", IF(E107&gt;=80, "A-", IF(E107&gt;=70, "B", IF(E107&gt;=50, "C", IF(E107&gt;=30, "D", "F")))))</f>
+        <v>A</v>
+      </c>
       <c r="H107" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="108" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B108" s="6" t="s">
         <v>51</v>
       </c>
@@ -3664,12 +3961,15 @@
       <c r="F108" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G108" s="12"/>
+      <c r="G108" s="12" t="str">
+        <f t="shared" ref="G108:G126" si="3">IF(E108&gt;=90, "A", IF(E108&gt;=80, "A-", IF(E108&gt;=70, "B", IF(E108&gt;=50, "C", IF(E108&gt;=30, "D", "F")))))</f>
+        <v>A-</v>
+      </c>
       <c r="H108" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B109" s="6" t="s">
         <v>52</v>
       </c>
@@ -3685,12 +3985,15 @@
       <c r="F109" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G109" s="12"/>
+      <c r="G109" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
       <c r="H109" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="6" t="s">
         <v>53</v>
       </c>
@@ -3706,12 +4009,15 @@
       <c r="F110" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G110" s="12"/>
+      <c r="G110" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
       <c r="H110" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="111" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B111" s="6" t="s">
         <v>54</v>
       </c>
@@ -3727,12 +4033,15 @@
       <c r="F111" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G111" s="12"/>
+      <c r="G111" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
+      </c>
       <c r="H111" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="112" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B112" s="6" t="s">
         <v>55</v>
       </c>
@@ -3748,12 +4057,15 @@
       <c r="F112" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G112" s="12"/>
+      <c r="G112" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
       <c r="H112" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="113" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="6" t="s">
         <v>29</v>
       </c>
@@ -3769,12 +4081,15 @@
       <c r="F113" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G113" s="12"/>
+      <c r="G113" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
       <c r="H113" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="114" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="6" t="s">
         <v>56</v>
       </c>
@@ -3790,12 +4105,15 @@
       <c r="F114" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G114" s="12"/>
+      <c r="G114" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
+      </c>
       <c r="H114" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="115" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="6" t="s">
         <v>28</v>
       </c>
@@ -3811,12 +4129,15 @@
       <c r="F115" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G115" s="12"/>
+      <c r="G115" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
       <c r="H115" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="116" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B116" s="6" t="s">
         <v>30</v>
       </c>
@@ -3832,12 +4153,15 @@
       <c r="F116" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G116" s="12"/>
+      <c r="G116" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
       <c r="H116" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="117" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B117" s="6" t="s">
         <v>31</v>
       </c>
@@ -3853,12 +4177,15 @@
       <c r="F117" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G117" s="12"/>
+      <c r="G117" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>A-</v>
+      </c>
       <c r="H117" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="118" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B118" s="6" t="s">
         <v>57</v>
       </c>
@@ -3874,12 +4201,15 @@
       <c r="F118" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G118" s="12"/>
+      <c r="G118" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
       <c r="H118" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="119" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B119" s="6" t="s">
         <v>27</v>
       </c>
@@ -3895,12 +4225,15 @@
       <c r="F119" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G119" s="12"/>
+      <c r="G119" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>A-</v>
+      </c>
       <c r="H119" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="120" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="6" t="s">
         <v>58</v>
       </c>
@@ -3916,12 +4249,15 @@
       <c r="F120" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G120" s="12"/>
+      <c r="G120" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
+      </c>
       <c r="H120" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="121" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B121" s="6" t="s">
         <v>59</v>
       </c>
@@ -3937,12 +4273,15 @@
       <c r="F121" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G121" s="12"/>
+      <c r="G121" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
+      </c>
       <c r="H121" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="122" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B122" s="6" t="s">
         <v>60</v>
       </c>
@@ -3958,12 +4297,15 @@
       <c r="F122" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G122" s="12"/>
+      <c r="G122" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
       <c r="H122" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B123" s="6" t="s">
         <v>61</v>
       </c>
@@ -3979,12 +4321,15 @@
       <c r="F123" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G123" s="12"/>
+      <c r="G123" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
       <c r="H123" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="124" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B124" s="6" t="s">
         <v>62</v>
       </c>
@@ -4000,12 +4345,15 @@
       <c r="F124" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G124" s="12"/>
+      <c r="G124" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>F</v>
+      </c>
       <c r="H124" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="125" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B125" s="6" t="s">
         <v>63</v>
       </c>
@@ -4021,12 +4369,15 @@
       <c r="F125" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G125" s="12"/>
+      <c r="G125" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
+      </c>
       <c r="H125" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="126" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="6" t="s">
         <v>64</v>
       </c>
@@ -4042,7 +4393,10 @@
       <c r="F126" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G126" s="12"/>
+      <c r="G126" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>A-</v>
+      </c>
       <c r="H126" s="17" t="s">
         <v>88</v>
       </c>
